--- a/data/trans_camb/P20-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P20-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,62</t>
+          <t>-3,0; 2,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,01</t>
+          <t>-2,06; 4,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,43</t>
+          <t>-1,6; 4,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 9,34</t>
+          <t>0,11; 9,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,81</t>
+          <t>-0,52; 7,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,86</t>
+          <t>-2,55; 4,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,83</t>
+          <t>-0,43; 4,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,69</t>
+          <t>-0,46; 4,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,3</t>
+          <t>-1,28; 3,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 73,41</t>
+          <t>-49,24; 79,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 105,55</t>
+          <t>-31,65; 127,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 123,47</t>
+          <t>-26,41; 135,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 204,72</t>
+          <t>-1,42; 213,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 174,73</t>
+          <t>-9,03; 184,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 91,32</t>
+          <t>-30,2; 109,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 106,96</t>
+          <t>-8,36; 106,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 104,02</t>
+          <t>-7,36; 107,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 73,92</t>
+          <t>-19,28; 77,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,63</t>
+          <t>-2,99; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,45</t>
+          <t>-1,83; 4,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,37</t>
+          <t>-2,39; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,59</t>
+          <t>-2,17; 6,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,61</t>
+          <t>-2,65; 5,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 3,17</t>
+          <t>-3,88; 3,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,31</t>
+          <t>-2,1; 3,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,92</t>
+          <t>-1,51; 3,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,11</t>
+          <t>-2,29; 2,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 95,56</t>
+          <t>-55,18; 96,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 151,31</t>
+          <t>-35,9; 177,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 117,65</t>
+          <t>-42,16; 132,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 113,18</t>
+          <t>-23,8; 108,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 94,95</t>
+          <t>-27,8; 92,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 52,79</t>
+          <t>-40,25; 58,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 67,87</t>
+          <t>-28,59; 69,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 87,41</t>
+          <t>-20,03; 77,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 42,87</t>
+          <t>-31,22; 43,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,05</t>
+          <t>1,08; 6,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,84</t>
+          <t>-0,22; 4,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,55</t>
+          <t>-3,49; 4,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 4,8</t>
+          <t>-8,07; 4,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,59</t>
+          <t>-7,03; 6,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 6,82</t>
+          <t>-6,22; 6,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,14</t>
+          <t>0,23; 5,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,36</t>
+          <t>-0,95; 4,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,7</t>
+          <t>-3,76; 3,59</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,12; 251,91</t>
+          <t>18,33; 234,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 178,36</t>
+          <t>-9,66; 162,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 132,72</t>
+          <t>-61,99; 124,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,43; 76,45</t>
+          <t>-56,63; 70,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 130,65</t>
+          <t>-55,55; 114,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 114,76</t>
+          <t>-49,14; 113,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,02; 128,07</t>
+          <t>3,76; 133,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 102,52</t>
+          <t>-13,96; 101,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 78,04</t>
+          <t>-58,95; 74,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,65</t>
+          <t>-0,13; 3,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,92</t>
+          <t>-1,74; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,37</t>
+          <t>-0,56; 3,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,86</t>
+          <t>-1,11; 5,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,21</t>
+          <t>-2,48; 3,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,41</t>
+          <t>-7,07; -0,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,71</t>
+          <t>0,32; 3,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,16</t>
+          <t>-1,04; 2,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,97</t>
+          <t>-2,5; 1,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 96,77</t>
+          <t>-2,28; 102,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 53,82</t>
+          <t>-32,04; 45,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 92,88</t>
+          <t>-11,33; 86,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 62,72</t>
+          <t>-11,61; 66,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 44,35</t>
+          <t>-24,3; 43,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,17; -8,26</t>
+          <t>-66,1; -8,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 70,26</t>
+          <t>4,95; 66,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 40,71</t>
+          <t>-14,75; 40,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 17,1</t>
+          <t>-37,44; 19,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,47</t>
+          <t>-0,13; 6,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,5</t>
+          <t>-3,89; 1,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,26</t>
+          <t>0,74; 7,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,34</t>
+          <t>-0,15; 6,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,02</t>
+          <t>-4,1; 1,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,43</t>
+          <t>-4,73; 0,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,52</t>
+          <t>0,59; 5,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,88</t>
+          <t>-3,19; 0,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,12</t>
+          <t>-2,33; 1,93</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,39; 232,38</t>
+          <t>-8,24; 202,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,14; 52,08</t>
+          <t>-61,85; 58,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,92; 259,75</t>
+          <t>10,53; 260,02</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 116,82</t>
+          <t>-3,7; 107,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 35,93</t>
+          <t>-44,66; 27,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 8,41</t>
+          <t>-55,46; 9,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,8; 111,5</t>
+          <t>5,6; 104,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 19,7</t>
+          <t>-42,97; 17,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 42,93</t>
+          <t>-31,9; 38,54</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,34</t>
+          <t>-0,49; 4,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,51</t>
+          <t>-0,38; 4,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,11</t>
+          <t>-2,18; 2,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,24</t>
+          <t>-0,81; 3,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,68</t>
+          <t>-2,33; 1,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,91</t>
+          <t>-3,07; 0,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,23</t>
+          <t>-0,58; 2,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,66</t>
+          <t>-1,48; 1,84</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,6</t>
+          <t>-2,82; 0,52</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 1249,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 1308,04</t>
+          <t>-52,14; 1186,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 56,6</t>
+          <t>-11,62; 61,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 28,95</t>
+          <t>-32,81; 32,01</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 15,09</t>
+          <t>-42,01; 17,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 70,32</t>
+          <t>-9,58; 64,38</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 34,1</t>
+          <t>-24,33; 39,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 13,64</t>
+          <t>-45,81; 10,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,94</t>
+          <t>0,78; 2,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,68</t>
+          <t>-0,33; 1,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,51</t>
+          <t>-0,01; 2,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,54</t>
+          <t>0,81; 3,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,67</t>
+          <t>-0,91; 1,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; -0,18</t>
+          <t>-2,94; -0,28</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,81</t>
+          <t>1,15; 2,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,33</t>
+          <t>-0,33; 1,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,83</t>
+          <t>-1,04; 0,83</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,62; 80,56</t>
+          <t>17,19; 78,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 47,22</t>
+          <t>-6,96; 46,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 66,79</t>
+          <t>0,05; 67,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,06; 52,6</t>
+          <t>9,67; 48,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 25,19</t>
+          <t>-11,32; 24,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,54; -2,79</t>
+          <t>-37,0; -4,07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,34; 52,05</t>
+          <t>18,3; 55,02</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 25,0</t>
+          <t>-5,99; 25,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 14,96</t>
+          <t>-16,87; 15,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P20-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,99</t>
+          <t>-3,27; 2,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,34</t>
+          <t>-1,87; 4,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,6</t>
+          <t>-1,89; 3,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,68</t>
+          <t>0,1; 9,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 7,73</t>
+          <t>-0,8; 7,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,57</t>
+          <t>-3,24; 4,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,74</t>
+          <t>-0,64; 4,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,88</t>
+          <t>-0,51; 4,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,3</t>
+          <t>-0,97; 3,27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 79,86</t>
+          <t>-50,29; 78,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,65; 127,46</t>
+          <t>-31,42; 127,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 135,94</t>
+          <t>-29,79; 99,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 213,37</t>
+          <t>-1,23; 217,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 184,1</t>
+          <t>-12,49; 200,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 109,51</t>
+          <t>-36,56; 94,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 106,03</t>
+          <t>-9,95; 101,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 107,91</t>
+          <t>-7,5; 102,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 77,73</t>
+          <t>-15,29; 76,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,66</t>
+          <t>-2,93; 2,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,74</t>
+          <t>-1,83; 4,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,29</t>
+          <t>-2,17; 3,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,7</t>
+          <t>-2,37; 6,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,5</t>
+          <t>-3,43; 5,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,23</t>
+          <t>-3,61; 3,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,25</t>
+          <t>-2,16; 3,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,76</t>
+          <t>-1,06; 4,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,08</t>
+          <t>-2,03; 2,34</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,48%</t>
+          <t>-0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 96,88</t>
+          <t>-52,53; 124,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 177,32</t>
+          <t>-37,49; 163,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 132,8</t>
+          <t>-37,01; 122,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 108,28</t>
+          <t>-25,31; 103,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 92,48</t>
+          <t>-34,64; 84,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 58,99</t>
+          <t>-36,7; 62,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 69,56</t>
+          <t>-27,6; 78,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 77,44</t>
+          <t>-15,8; 81,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 43,74</t>
+          <t>-27,88; 50,03</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>3,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,67</t>
+          <t>1,16; 6,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,9</t>
+          <t>-0,24; 4,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,38</t>
+          <t>1,0; 6,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 4,37</t>
+          <t>-7,98; 4,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 6,95</t>
+          <t>-7,51; 6,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 6,39</t>
+          <t>-6,29; 7,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,31</t>
+          <t>0,25; 5,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,31</t>
+          <t>-0,95; 4,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,59</t>
+          <t>0,39; 5,81</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,33%</t>
+          <t>-0,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,33; 234,45</t>
+          <t>21,78; 227,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 162,72</t>
+          <t>-8,65; 174,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 124,18</t>
+          <t>15,52; 234,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 70,4</t>
+          <t>-54,77; 65,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 114,15</t>
+          <t>-57,19; 108,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 113,29</t>
+          <t>-48,09; 135,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,76; 133,27</t>
+          <t>2,31; 125,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 101,39</t>
+          <t>-16,9; 105,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 74,76</t>
+          <t>5,81; 138,26</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,82</t>
+          <t>0,01; 3,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,77</t>
+          <t>-1,78; 1,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,27</t>
+          <t>-0,97; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,0</t>
+          <t>-1,32; 4,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,28</t>
+          <t>-2,44; 3,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -0,61</t>
+          <t>-4,82; 0,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,56</t>
+          <t>0,35; 3,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,14</t>
+          <t>-1,09; 2,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,08</t>
+          <t>-1,46; 1,58</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-39,5%</t>
+          <t>-21,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 102,32</t>
+          <t>-0,98; 98,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 45,52</t>
+          <t>-32,7; 48,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 86,96</t>
+          <t>-17,26; 72,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 66,38</t>
+          <t>-12,97; 67,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 43,97</t>
+          <t>-23,79; 48,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,1; -8,45</t>
+          <t>-45,54; 8,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 66,14</t>
+          <t>5,03; 66,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 40,21</t>
+          <t>-15,42; 39,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 19,55</t>
+          <t>-20,46; 29,46</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 6,2</t>
+          <t>0,02; 6,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,47</t>
+          <t>-3,72; 1,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,1</t>
+          <t>0,43; 6,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 6,2</t>
+          <t>0,04; 6,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,63</t>
+          <t>-3,61; 2,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,46</t>
+          <t>-4,29; 1,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,4</t>
+          <t>0,75; 5,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,84</t>
+          <t>-3,06; 0,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,93</t>
+          <t>-1,63; 2,28</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,11%</t>
+          <t>-21,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 202,42</t>
+          <t>-3,75; 233,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-61,85; 58,68</t>
+          <t>-58,83; 63,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10,53; 260,02</t>
+          <t>6,26; 223,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 107,15</t>
+          <t>-1,48; 117,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 27,11</t>
+          <t>-41,47; 38,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 9,03</t>
+          <t>-47,86; 20,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,6; 104,15</t>
+          <t>9,62; 110,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 17,8</t>
+          <t>-42,11; 17,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 38,54</t>
+          <t>-22,61; 47,03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-0,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,3</t>
+          <t>-0,48; 4,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,59</t>
+          <t>-0,47; 4,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,36</t>
+          <t>-1,61; 3,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,32</t>
+          <t>-0,73; 3,39</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,71</t>
+          <t>-2,33; 1,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,9</t>
+          <t>-3,21; 0,71</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,98</t>
+          <t>-0,49; 3,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,84</t>
+          <t>-1,6; 1,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,52</t>
+          <t>-2,62; 0,84</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-1,54%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-17,2%</t>
+          <t>-19,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-20,15%</t>
+          <t>-18,2%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-62,05; 1210,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 1186,45</t>
+          <t>-64,61; 1116,42</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1097,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 61,73</t>
+          <t>-9,96; 60,16</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 32,01</t>
+          <t>-32,88; 30,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-42,01; 17,06</t>
+          <t>-44,2; 13,39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 64,38</t>
+          <t>-8,4; 67,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 39,97</t>
+          <t>-25,53; 40,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-45,81; 10,91</t>
+          <t>-42,1; 19,87</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,91</t>
+          <t>0,89; 3,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,69</t>
+          <t>-0,27; 1,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,56</t>
+          <t>0,79; 2,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,35</t>
+          <t>0,75; 3,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,68</t>
+          <t>-0,95; 1,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,28</t>
+          <t>-2,01; 0,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,96</t>
+          <t>1,15; 2,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,39</t>
+          <t>-0,33; 1,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,83</t>
+          <t>-0,39; 1,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-20,26%</t>
+          <t>-11,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-1,14%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,19; 78,26</t>
+          <t>19,26; 87,52</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 46,48</t>
+          <t>-5,32; 45,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,05; 67,05</t>
+          <t>16,85; 80,83</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,67; 48,66</t>
+          <t>9,28; 52,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 24,58</t>
+          <t>-12,03; 25,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,0; -4,07</t>
+          <t>-24,99; 5,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,3; 55,02</t>
+          <t>18,0; 53,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 25,23</t>
+          <t>-5,33; 25,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 15,48</t>
+          <t>-6,44; 24,81</t>
         </is>
       </c>
     </row>
